--- a/resources/templates/standard/L1100-22.xlsx
+++ b/resources/templates/standard/L1100-22.xlsx
@@ -11,7 +11,10 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="35">
+  <si>
+    <t>{{companyLogo}}</t>
+  </si>
   <si>
     <t xml:space="preserve">결
 재</t>
@@ -623,7 +626,9 @@
   <sheetFormatPr defaultRowHeight="20.15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="3.08203125" customHeight="1"/>
   <sheetData>
     <row r="1" ht="20.15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A1" s="1"/>
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
       <c r="D1" s="2"/>
@@ -646,15 +651,15 @@
       <c r="U1" s="2"/>
       <c r="V1" s="2"/>
       <c r="W1" s="3" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X1" s="4" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y1" s="4"/>
       <c r="Z1" s="4"/>
       <c r="AA1" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AB1" s="4"/>
       <c r="AC1" s="4"/>
@@ -723,7 +728,7 @@
     </row>
     <row r="4" ht="20.15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A4" s="6" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B4" s="6"/>
       <c r="C4" s="6"/>
@@ -756,44 +761,44 @@
     </row>
     <row r="5" ht="20.15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A5" s="7" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B5" s="7"/>
       <c r="C5" s="7"/>
       <c r="D5" s="7"/>
       <c r="E5" s="7"/>
       <c r="F5" s="8" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G5" s="8"/>
       <c r="H5" s="8"/>
       <c r="I5" s="8"/>
       <c r="J5" s="8" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K5" s="8"/>
       <c r="L5" s="8"/>
       <c r="M5" s="8"/>
       <c r="N5" s="8" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="O5" s="8"/>
       <c r="P5" s="8"/>
       <c r="Q5" s="8"/>
       <c r="R5" s="8" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="S5" s="8"/>
       <c r="T5" s="8"/>
       <c r="U5" s="8"/>
       <c r="V5" s="8" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W5" s="8"/>
       <c r="X5" s="8"/>
       <c r="Y5" s="8"/>
       <c r="Z5" s="8" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA5" s="8"/>
       <c r="AB5" s="8"/>
@@ -801,7 +806,7 @@
     </row>
     <row r="6" ht="20.15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A6" s="9" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B6" s="9"/>
       <c r="C6" s="9"/>
@@ -834,7 +839,7 @@
     </row>
     <row r="7" ht="20.15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A7" s="9" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B7" s="9"/>
       <c r="C7" s="9"/>
@@ -867,7 +872,7 @@
     </row>
     <row r="8" ht="20.15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A8" s="9" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B8" s="9"/>
       <c r="C8" s="9"/>
@@ -962,7 +967,7 @@
     </row>
     <row r="11" ht="20.15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A11" s="12" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B11" s="12"/>
       <c r="C11" s="12"/>
@@ -995,44 +1000,44 @@
     </row>
     <row r="12" ht="20.15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A12" s="7" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B12" s="7"/>
       <c r="C12" s="7"/>
       <c r="D12" s="7"/>
       <c r="E12" s="7"/>
       <c r="F12" s="8" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G12" s="8"/>
       <c r="H12" s="8"/>
       <c r="I12" s="8"/>
       <c r="J12" s="8" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K12" s="8"/>
       <c r="L12" s="8"/>
       <c r="M12" s="8"/>
       <c r="N12" s="8" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="O12" s="8"/>
       <c r="P12" s="8"/>
       <c r="Q12" s="8"/>
       <c r="R12" s="8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="S12" s="8"/>
       <c r="T12" s="8"/>
       <c r="U12" s="8"/>
       <c r="V12" s="8" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="W12" s="8"/>
       <c r="X12" s="8"/>
       <c r="Y12" s="8"/>
       <c r="Z12" s="8" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AA12" s="8"/>
       <c r="AB12" s="8"/>
@@ -1040,7 +1045,7 @@
     </row>
     <row r="13" ht="20.15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A13" s="9" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B13" s="9"/>
       <c r="C13" s="9"/>
@@ -1073,7 +1078,7 @@
     </row>
     <row r="14" ht="20.15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A14" s="9" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B14" s="9"/>
       <c r="C14" s="9"/>
@@ -1106,7 +1111,7 @@
     </row>
     <row r="15" ht="20.15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A15" s="9" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B15" s="9"/>
       <c r="C15" s="9"/>
@@ -1201,38 +1206,38 @@
     </row>
     <row r="18" ht="20.15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A18" s="12" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B18" s="12"/>
       <c r="C18" s="12"/>
       <c r="D18" s="12"/>
       <c r="E18" s="12"/>
       <c r="F18" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G18" s="13"/>
       <c r="H18" s="13"/>
       <c r="I18" s="13"/>
       <c r="J18" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K18" s="13"/>
       <c r="L18" s="13"/>
       <c r="M18" s="13"/>
       <c r="N18" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="O18" s="13"/>
       <c r="P18" s="13"/>
       <c r="Q18" s="13"/>
       <c r="R18" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="S18" s="13"/>
       <c r="T18" s="13"/>
       <c r="U18" s="13"/>
       <c r="V18" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="W18" s="13"/>
       <c r="X18" s="13"/>
@@ -1244,44 +1249,44 @@
     </row>
     <row r="19" ht="20.15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A19" s="7" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B19" s="7"/>
       <c r="C19" s="7"/>
       <c r="D19" s="7"/>
       <c r="E19" s="7"/>
       <c r="F19" s="8" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G19" s="8"/>
       <c r="H19" s="8"/>
       <c r="I19" s="8"/>
       <c r="J19" s="8" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K19" s="8"/>
       <c r="L19" s="8"/>
       <c r="M19" s="8"/>
       <c r="N19" s="8" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="O19" s="8"/>
       <c r="P19" s="8"/>
       <c r="Q19" s="8"/>
       <c r="R19" s="8" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="S19" s="8"/>
       <c r="T19" s="8"/>
       <c r="U19" s="8"/>
       <c r="V19" s="8" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="W19" s="8"/>
       <c r="X19" s="8"/>
       <c r="Y19" s="8"/>
       <c r="Z19" s="8" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AA19" s="8"/>
       <c r="AB19" s="8"/>
@@ -1289,38 +1294,38 @@
     </row>
     <row r="20" ht="20.15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A20" s="9" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B20" s="9"/>
       <c r="C20" s="9"/>
       <c r="D20" s="9"/>
       <c r="E20" s="9"/>
       <c r="F20" s="10" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G20" s="10"/>
       <c r="H20" s="10"/>
       <c r="I20" s="10"/>
       <c r="J20" s="10" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K20" s="10"/>
       <c r="L20" s="10"/>
       <c r="M20" s="10"/>
       <c r="N20" s="10" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="O20" s="10"/>
       <c r="P20" s="10"/>
       <c r="Q20" s="10"/>
       <c r="R20" s="10" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="S20" s="10"/>
       <c r="T20" s="10"/>
       <c r="U20" s="10"/>
       <c r="V20" s="10" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="W20" s="10"/>
       <c r="X20" s="10"/>
@@ -1332,7 +1337,7 @@
     </row>
     <row r="21" ht="20.15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A21" s="9" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B21" s="9"/>
       <c r="C21" s="9"/>
@@ -1365,7 +1370,7 @@
     </row>
     <row r="22" ht="20.15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A22" s="9" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B22" s="9"/>
       <c r="C22" s="9"/>
@@ -1460,38 +1465,38 @@
     </row>
     <row r="25" ht="20.15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A25" s="12" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B25" s="12"/>
       <c r="C25" s="12"/>
       <c r="D25" s="12"/>
       <c r="E25" s="12"/>
       <c r="F25" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G25" s="13"/>
       <c r="H25" s="13"/>
       <c r="I25" s="13"/>
       <c r="J25" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K25" s="13"/>
       <c r="L25" s="13"/>
       <c r="M25" s="13"/>
       <c r="N25" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="O25" s="13"/>
       <c r="P25" s="13"/>
       <c r="Q25" s="13"/>
       <c r="R25" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="S25" s="13"/>
       <c r="T25" s="13"/>
       <c r="U25" s="13"/>
       <c r="V25" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="W25" s="13"/>
       <c r="X25" s="13"/>
@@ -1503,26 +1508,26 @@
     </row>
     <row r="26" ht="20.15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A26" s="7" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B26" s="7"/>
       <c r="C26" s="7"/>
       <c r="D26" s="7"/>
       <c r="E26" s="7"/>
       <c r="F26" s="8" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G26" s="8"/>
       <c r="H26" s="8"/>
       <c r="I26" s="8"/>
       <c r="J26" s="8" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="K26" s="8"/>
       <c r="L26" s="8"/>
       <c r="M26" s="8"/>
       <c r="N26" s="8" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="O26" s="8"/>
       <c r="P26" s="8"/>
@@ -1542,20 +1547,20 @@
     </row>
     <row r="27" ht="20.15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A27" s="9" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B27" s="9"/>
       <c r="C27" s="9"/>
       <c r="D27" s="9"/>
       <c r="E27" s="9"/>
       <c r="F27" s="10" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G27" s="10"/>
       <c r="H27" s="10"/>
       <c r="I27" s="10"/>
       <c r="J27" s="10" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K27" s="10"/>
       <c r="L27" s="10"/>
@@ -1579,7 +1584,7 @@
     </row>
     <row r="28" ht="20.15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A28" s="9" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B28" s="9"/>
       <c r="C28" s="9"/>
@@ -1612,7 +1617,7 @@
     </row>
     <row r="29" ht="20.15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A29" s="9" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B29" s="9"/>
       <c r="C29" s="9"/>
@@ -1707,20 +1712,20 @@
     </row>
     <row r="32" ht="20.15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A32" s="12" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B32" s="12"/>
       <c r="C32" s="12"/>
       <c r="D32" s="12"/>
       <c r="E32" s="12"/>
       <c r="F32" s="10" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G32" s="10"/>
       <c r="H32" s="10"/>
       <c r="I32" s="10"/>
       <c r="J32" s="10" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K32" s="10"/>
       <c r="L32" s="10"/>
@@ -1744,44 +1749,44 @@
     </row>
     <row r="33" ht="20.15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A33" s="7" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B33" s="7"/>
       <c r="C33" s="7"/>
       <c r="D33" s="7"/>
       <c r="E33" s="7"/>
       <c r="F33" s="8" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G33" s="8"/>
       <c r="H33" s="8"/>
       <c r="I33" s="8"/>
       <c r="J33" s="8" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K33" s="8"/>
       <c r="L33" s="8"/>
       <c r="M33" s="8"/>
       <c r="N33" s="8" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="O33" s="8"/>
       <c r="P33" s="8"/>
       <c r="Q33" s="8"/>
       <c r="R33" s="8" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="S33" s="8"/>
       <c r="T33" s="8"/>
       <c r="U33" s="8"/>
       <c r="V33" s="8" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="W33" s="8"/>
       <c r="X33" s="8"/>
       <c r="Y33" s="8"/>
       <c r="Z33" s="8" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AA33" s="8"/>
       <c r="AB33" s="8"/>
@@ -1789,38 +1794,38 @@
     </row>
     <row r="34" ht="20.15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A34" s="9" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B34" s="9"/>
       <c r="C34" s="9"/>
       <c r="D34" s="9"/>
       <c r="E34" s="9"/>
       <c r="F34" s="10" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G34" s="10"/>
       <c r="H34" s="10"/>
       <c r="I34" s="10"/>
       <c r="J34" s="10" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K34" s="10"/>
       <c r="L34" s="10"/>
       <c r="M34" s="10"/>
       <c r="N34" s="10" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="O34" s="10"/>
       <c r="P34" s="10"/>
       <c r="Q34" s="10"/>
       <c r="R34" s="10" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="S34" s="10"/>
       <c r="T34" s="10"/>
       <c r="U34" s="10"/>
       <c r="V34" s="10" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="W34" s="10"/>
       <c r="X34" s="10"/>
@@ -1832,7 +1837,7 @@
     </row>
     <row r="35" ht="20.15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A35" s="9" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B35" s="9"/>
       <c r="C35" s="9"/>
@@ -1865,7 +1870,7 @@
     </row>
     <row r="36" ht="20.15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A36" s="9" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B36" s="9"/>
       <c r="C36" s="9"/>
@@ -1960,38 +1965,38 @@
     </row>
     <row r="39" ht="20.15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A39" s="12" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B39" s="12"/>
       <c r="C39" s="12"/>
       <c r="D39" s="12"/>
       <c r="E39" s="12"/>
       <c r="F39" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G39" s="13"/>
       <c r="H39" s="13"/>
       <c r="I39" s="13"/>
       <c r="J39" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K39" s="13"/>
       <c r="L39" s="13"/>
       <c r="M39" s="13"/>
       <c r="N39" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="O39" s="13"/>
       <c r="P39" s="13"/>
       <c r="Q39" s="13"/>
       <c r="R39" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="S39" s="13"/>
       <c r="T39" s="13"/>
       <c r="U39" s="13"/>
       <c r="V39" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="W39" s="13"/>
       <c r="X39" s="13"/>
